--- a/Overpotnital/O2 BP/BOL/Edited/AB BM 1.5bp O2_edited.xlsx
+++ b/Overpotnital/O2 BP/BOL/Edited/AB BM 1.5bp O2_edited.xlsx
@@ -638,7 +638,7 @@
       <c r="A4" s="0" t="n">
         <v>0.09621045</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="0" t="n">
         <v>0.89314</v>
       </c>
       <c r="C4" s="0">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.49</v>
+        <v>-0.498</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -728,7 +728,7 @@
       <c r="A5" s="0" t="n">
         <v>0.1978303</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="0" t="n">
         <v>0.86927</v>
       </c>
       <c r="C5" s="0">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.04266</v>
+        <v>-0.0427</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -810,7 +810,7 @@
       <c r="A6" s="0" t="n">
         <v>0.29656735</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>0.85267</v>
       </c>
       <c r="C6" s="0">
@@ -889,7 +889,7 @@
       <c r="A7" s="0" t="n">
         <v>0.3974665</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>0.83943</v>
       </c>
       <c r="C7" s="0">
@@ -972,7 +972,7 @@
       <c r="A8" s="0" t="n">
         <v>0.49620355</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="0" t="n">
         <v>0.82803</v>
       </c>
       <c r="C8" s="0">
@@ -1046,7 +1046,7 @@
       <c r="A9" s="0" t="n">
         <v>0.596382</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="0" t="n">
         <v>0.8178299999999999</v>
       </c>
       <c r="C9" s="0">
@@ -1128,7 +1128,7 @@
       <c r="A10" s="0" t="n">
         <v>0.69583975</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="0" t="n">
         <v>0.80857</v>
       </c>
       <c r="C10" s="0">
@@ -1202,7 +1202,7 @@
       <c r="A11" s="0" t="n">
         <v>0.79529755</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>0.79992</v>
       </c>
       <c r="C11" s="0">
@@ -1285,7 +1285,7 @@
       <c r="A12" s="0" t="n">
         <v>0.8961967</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="0" t="n">
         <v>0.7918500000000001</v>
       </c>
       <c r="C12" s="0">
@@ -1363,7 +1363,7 @@
       <c r="A13" s="0" t="n">
         <v>0.99421305</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>0.7841</v>
       </c>
       <c r="C13" s="0">
@@ -1437,7 +1437,7 @@
       <c r="A14" s="0" t="n">
         <v>1.09583295</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>0.77669</v>
       </c>
       <c r="C14" s="0">
@@ -1511,7 +1511,7 @@
       <c r="A15" s="0" t="n">
         <v>1.1952907</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>0.76956</v>
       </c>
       <c r="C15" s="0">
@@ -1585,7 +1585,7 @@
       <c r="A16" s="0" t="n">
         <v>1.29474845</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="0" t="n">
         <v>0.76262</v>
       </c>
       <c r="C16" s="0">
@@ -1659,7 +1659,7 @@
       <c r="A17" s="0" t="n">
         <v>1.39636825</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>0.7559</v>
       </c>
       <c r="C17" s="0">
@@ -1733,7 +1733,7 @@
       <c r="A18" s="0" t="n">
         <v>1.4929433</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="0" t="n">
         <v>0.74946</v>
       </c>
       <c r="C18" s="0">
@@ -1807,7 +1807,7 @@
       <c r="A19" s="0" t="n">
         <v>1.59312165</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>0.7430600000000001</v>
       </c>
       <c r="C19" s="0">
@@ -1881,7 +1881,7 @@
       <c r="A20" s="0" t="n">
         <v>1.6947416</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>0.73686</v>
       </c>
       <c r="C20" s="0">
@@ -1955,7 +1955,7 @@
       <c r="A21" s="0" t="n">
         <v>1.79203725</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>0.7308</v>
       </c>
       <c r="C21" s="0">
@@ -2029,7 +2029,7 @@
       <c r="A22" s="0" t="n">
         <v>1.8958192</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>0.72487</v>
       </c>
       <c r="C22" s="0">
@@ -2103,7 +2103,7 @@
       <c r="A23" s="0" t="n">
         <v>1.9945562</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="0" t="n">
         <v>0.7190800000000001</v>
       </c>
       <c r="C23" s="0">
@@ -2177,7 +2177,7 @@
       <c r="A24" s="0" t="n">
         <v>2.0932932</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="0" t="n">
         <v>0.71347</v>
       </c>
       <c r="C24" s="0">
@@ -2251,7 +2251,7 @@
       <c r="A25" s="0" t="n">
         <v>2.19275095</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="0" t="n">
         <v>0.708</v>
       </c>
       <c r="C25" s="0">
@@ -2325,7 +2325,7 @@
       <c r="A26" s="0" t="n">
         <v>2.2929294</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="0" t="n">
         <v>0.70265</v>
       </c>
       <c r="C26" s="0">
@@ -2399,7 +2399,7 @@
       <c r="A27" s="0" t="n">
         <v>2.39166665</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="0" t="n">
         <v>0.69743</v>
       </c>
       <c r="C27" s="0">
@@ -2473,7 +2473,7 @@
       <c r="A28" s="0" t="n">
         <v>2.49184515</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="0" t="n">
         <v>0.6923</v>
       </c>
       <c r="C28" s="0">
@@ -2547,7 +2547,7 @@
       <c r="A29" s="0" t="n">
         <v>2.59202335</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="0" t="n">
         <v>0.68726</v>
       </c>
       <c r="C29" s="0">
@@ -2621,7 +2621,7 @@
       <c r="A30" s="0" t="n">
         <v>2.6907606</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="0" t="n">
         <v>0.68236</v>
       </c>
       <c r="C30" s="0">
@@ -2695,7 +2695,7 @@
       <c r="A31" s="0" t="n">
         <v>2.7909391</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="0" t="n">
         <v>0.67762</v>
       </c>
       <c r="C31" s="0">
@@ -2769,7 +2769,7 @@
       <c r="A32" s="0" t="n">
         <v>2.8896761</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="0" t="n">
         <v>0.6729000000000001</v>
       </c>
       <c r="C32" s="0">
@@ -2836,7 +2836,7 @@
       <c r="A33" s="0" t="n">
         <v>2.98985455</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="0" t="n">
         <v>0.6682900000000001</v>
       </c>
       <c r="C33" s="0">
@@ -2903,7 +2903,7 @@
       <c r="A34" s="0" t="n">
         <v>3.09003305</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="0" t="n">
         <v>0.66368</v>
       </c>
       <c r="C34" s="0">
@@ -2970,7 +2970,7 @@
       <c r="A35" s="0" t="n">
         <v>3.18877005</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="0" t="n">
         <v>0.65921</v>
       </c>
       <c r="C35" s="0">
@@ -3037,7 +3037,7 @@
       <c r="A36" s="0" t="n">
         <v>3.2896693</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="0" t="n">
         <v>0.6547500000000001</v>
       </c>
       <c r="C36" s="0">
@@ -3104,7 +3104,7 @@
       <c r="A37" s="0" t="n">
         <v>3.389127</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="0" t="n">
         <v>0.65037</v>
       </c>
       <c r="C37" s="0">
@@ -3171,7 +3171,7 @@
       <c r="A38" s="0" t="n">
         <v>3.48858475</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="0" t="n">
         <v>0.64607</v>
       </c>
       <c r="C38" s="0">
@@ -3238,7 +3238,7 @@
       <c r="A39" s="0" t="n">
         <v>3.58876325</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="0" t="n">
         <v>0.64179</v>
       </c>
       <c r="C39" s="0">
@@ -3305,7 +3305,7 @@
       <c r="A40" s="0" t="n">
         <v>3.6889417</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="0" t="n">
         <v>0.63757</v>
       </c>
       <c r="C40" s="0">
@@ -3372,7 +3372,7 @@
       <c r="A41" s="0" t="n">
         <v>3.78839945</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="0" t="n">
         <v>0.63343</v>
       </c>
       <c r="C41" s="0">
@@ -3439,7 +3439,7 @@
       <c r="A42" s="0" t="n">
         <v>3.8878572</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.62931</v>
       </c>
       <c r="C42" s="0">
@@ -3506,7 +3506,7 @@
       <c r="A43" s="0" t="n">
         <v>3.98587345</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="0" t="n">
         <v>0.62519</v>
       </c>
       <c r="C43" s="0">
@@ -3573,7 +3573,7 @@
       <c r="A44" s="0" t="n">
         <v>4.08677245</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="0" t="n">
         <v>0.62122</v>
       </c>
       <c r="C44" s="0">
@@ -3640,7 +3640,7 @@
       <c r="A45" s="0" t="n">
         <v>4.1855097</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="0" t="n">
         <v>0.61711</v>
       </c>
       <c r="C45" s="0">
@@ -3707,7 +3707,7 @@
       <c r="A46" s="0" t="n">
         <v>4.28352595</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="0" t="n">
         <v>0.61312</v>
       </c>
       <c r="C46" s="0">
@@ -3774,7 +3774,7 @@
       <c r="A47" s="0" t="n">
         <v>4.38442515</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="0" t="n">
         <v>0.6091299999999999</v>
       </c>
       <c r="C47" s="0">
@@ -3841,7 +3841,7 @@
       <c r="A48" s="0" t="n">
         <v>4.4860449</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="0" t="n">
         <v>0.60519</v>
       </c>
       <c r="C48" s="0">
@@ -3908,7 +3908,7 @@
       <c r="A49" s="0" t="n">
         <v>4.5840616</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="0" t="n">
         <v>0.60123</v>
       </c>
       <c r="C49" s="0">
@@ -3975,7 +3975,7 @@
       <c r="A50" s="0" t="n">
         <v>4.68351935</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="0" t="n">
         <v>0.5972499999999999</v>
       </c>
       <c r="C50" s="0">
@@ -4042,7 +4042,7 @@
       <c r="A51" s="0" t="n">
         <v>4.78153565</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="0" t="n">
         <v>0.5934</v>
       </c>
       <c r="C51" s="0">
@@ -4109,7 +4109,7 @@
       <c r="A52" s="0" t="n">
         <v>4.88315535</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="0" t="n">
         <v>0.58952</v>
       </c>
       <c r="C52" s="0">
@@ -4176,7 +4176,7 @@
       <c r="A53" s="0" t="n">
         <v>4.9833336</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="0" t="n">
         <v>0.58567</v>
       </c>
       <c r="C53" s="0">
@@ -4243,7 +4243,7 @@
       <c r="A54" s="0" t="n">
         <v>5.08135035</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="0" t="n">
         <v>0.58185</v>
       </c>
       <c r="C54" s="0">
@@ -4310,7 +4310,7 @@
       <c r="A55" s="0" t="n">
         <v>5.18224955</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="0" t="n">
         <v>0.57795</v>
       </c>
       <c r="C55" s="0">
@@ -4377,7 +4377,7 @@
       <c r="A56" s="0" t="n">
         <v>5.2809863</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="0" t="n">
         <v>0.57415</v>
       </c>
       <c r="C56" s="0">
@@ -4444,7 +4444,7 @@
       <c r="A57" s="0" t="n">
         <v>5.38116505</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="0" t="n">
         <v>0.57029</v>
       </c>
       <c r="C57" s="0">
@@ -4511,7 +4511,7 @@
       <c r="A58" s="0" t="n">
         <v>5.4799018</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="0" t="n">
         <v>0.56655</v>
       </c>
       <c r="C58" s="0">
@@ -4578,7 +4578,7 @@
       <c r="A59" s="0" t="n">
         <v>5.580801</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="0" t="n">
         <v>0.56272</v>
       </c>
       <c r="C59" s="0">
@@ -4645,7 +4645,7 @@
       <c r="A60" s="0" t="n">
         <v>5.67881725</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="0" t="n">
         <v>0.55893</v>
       </c>
       <c r="C60" s="0">
@@ -4712,7 +4712,7 @@
       <c r="A61" s="0" t="n">
         <v>5.78043745</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="0" t="n">
         <v>0.55513</v>
       </c>
       <c r="C61" s="0">
@@ -4779,7 +4779,7 @@
       <c r="A62" s="0" t="n">
         <v>5.87845375</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="0" t="n">
         <v>0.55141</v>
       </c>
       <c r="C62" s="0">
@@ -4846,7 +4846,7 @@
       <c r="A63" s="0" t="n">
         <v>5.97935295</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="0" t="n">
         <v>0.54761</v>
       </c>
       <c r="C63" s="0">
@@ -4913,7 +4913,7 @@
       <c r="A64" s="0" t="n">
         <v>6.0795312</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="0" t="n">
         <v>0.54384</v>
       </c>
       <c r="C64" s="0">
@@ -4980,7 +4980,7 @@
       <c r="A65" s="0" t="n">
         <v>6.17826845</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="0" t="n">
         <v>0.54011</v>
       </c>
       <c r="C65" s="0">
@@ -5047,7 +5047,7 @@
       <c r="A66" s="0" t="n">
         <v>6.2762847</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="0" t="n">
         <v>0.5363599999999999</v>
       </c>
       <c r="C66" s="0">
@@ -5114,7 +5114,7 @@
       <c r="A67" s="0" t="n">
         <v>6.3786254</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="0" t="n">
         <v>0.53266</v>
       </c>
       <c r="C67" s="0">
@@ -5181,7 +5181,7 @@
       <c r="A68" s="0" t="n">
         <v>6.47736215</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="0" t="n">
         <v>0.52889</v>
       </c>
       <c r="C68" s="0">
@@ -5248,7 +5248,7 @@
       <c r="A69" s="0" t="n">
         <v>6.57754085</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="0" t="n">
         <v>0.52523</v>
       </c>
       <c r="C69" s="0">
@@ -5315,7 +5315,7 @@
       <c r="A70" s="0" t="n">
         <v>6.6769986</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="0" t="n">
         <v>0.5214800000000001</v>
       </c>
       <c r="C70" s="0">
@@ -5382,7 +5382,7 @@
       <c r="A71" s="0" t="n">
         <v>6.77645635</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="0" t="n">
         <v>0.51775</v>
       </c>
       <c r="C71" s="0">
@@ -5449,7 +5449,7 @@
       <c r="A72" s="0" t="n">
         <v>6.8751931</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="0" t="n">
         <v>0.514</v>
       </c>
       <c r="C72" s="0">
@@ -5516,7 +5516,7 @@
       <c r="A73" s="0" t="n">
         <v>6.97465085</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="0" t="n">
         <v>0.5103</v>
       </c>
       <c r="C73" s="0">
@@ -5583,7 +5583,7 @@
       <c r="A74" s="0" t="n">
         <v>7.07699155</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>0.50657</v>
       </c>
       <c r="C74" s="0">
@@ -5650,7 +5650,7 @@
       <c r="A75" s="0" t="n">
         <v>7.1750078</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="0" t="n">
         <v>0.50286</v>
       </c>
       <c r="C75" s="0">
@@ -5717,7 +5717,7 @@
       <c r="A76" s="0" t="n">
         <v>7.27590705</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="0" t="n">
         <v>0.49916</v>
       </c>
       <c r="C76" s="0">
@@ -5784,7 +5784,7 @@
       <c r="A77" s="0" t="n">
         <v>7.3732028</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="0" t="n">
         <v>0.49549</v>
       </c>
       <c r="C77" s="0">
@@ -5851,7 +5851,7 @@
       <c r="A78" s="0" t="n">
         <v>7.4748225</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="0" t="n">
         <v>0.49175</v>
       </c>
       <c r="C78" s="0">
@@ -5918,7 +5918,7 @@
       <c r="A79" s="0" t="n">
         <v>7.5728388</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="0" t="n">
         <v>0.48802</v>
       </c>
       <c r="C79" s="0">
@@ -5985,7 +5985,7 @@
       <c r="A80" s="0" t="n">
         <v>7.6730175</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="0" t="n">
         <v>0.48434</v>
       </c>
       <c r="C80" s="0">
@@ -6052,7 +6052,7 @@
       <c r="A81" s="0" t="n">
         <v>7.77175425</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="0" t="n">
         <v>0.48059</v>
       </c>
       <c r="C81" s="0">
@@ -6119,7 +6119,7 @@
       <c r="A82" s="0" t="n">
         <v>7.87337445</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="0" t="n">
         <v>0.47692</v>
       </c>
       <c r="C82" s="0">
@@ -6186,7 +6186,7 @@
       <c r="A83" s="0" t="n">
         <v>7.9728322</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="0" t="n">
         <v>0.47321</v>
       </c>
       <c r="C83" s="0">
@@ -6253,7 +6253,7 @@
       <c r="A84" s="0" t="n">
         <v>8.07156945</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>0.46952</v>
       </c>
       <c r="C84" s="0">
@@ -6320,7 +6320,7 @@
       <c r="A85" s="0" t="n">
         <v>8.171027199999999</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="0" t="n">
         <v>0.46577</v>
       </c>
       <c r="C85" s="0">
@@ -6387,7 +6387,7 @@
       <c r="A86" s="0" t="n">
         <v>8.2704849</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="0" t="n">
         <v>0.46203</v>
       </c>
       <c r="C86" s="0">
@@ -6454,7 +6454,7 @@
       <c r="A87" s="0" t="n">
         <v>8.3706627</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="0" t="n">
         <v>0.45839</v>
       </c>
       <c r="C87" s="0">
@@ -6521,7 +6521,7 @@
       <c r="A88" s="0" t="n">
         <v>8.47012045</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="0" t="n">
         <v>0.45463</v>
       </c>
       <c r="C88" s="0">
@@ -6588,7 +6588,7 @@
       <c r="A89" s="0" t="n">
         <v>8.568858150000001</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="0" t="n">
         <v>0.45093</v>
       </c>
       <c r="C89" s="0">
@@ -6655,7 +6655,7 @@
       <c r="A90" s="0" t="n">
         <v>8.669756899999999</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="0" t="n">
         <v>0.44723</v>
       </c>
       <c r="C90" s="0">
@@ -6722,7 +6722,7 @@
       <c r="A91" s="0" t="n">
         <v>8.76921465</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="0" t="n">
         <v>0.44349</v>
       </c>
       <c r="C91" s="0">
@@ -6789,7 +6789,7 @@
       <c r="A92" s="0" t="n">
         <v>8.87011435</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="0" t="n">
         <v>0.43965</v>
       </c>
       <c r="C92" s="0">
@@ -6856,7 +6856,7 @@
       <c r="A93" s="0" t="n">
         <v>8.9688511</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="0" t="n">
         <v>0.43601</v>
       </c>
       <c r="C93" s="0">
@@ -6923,7 +6923,7 @@
       <c r="A94" s="0" t="n">
         <v>9.067587850000001</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="0" t="n">
         <v>0.43236</v>
       </c>
       <c r="C94" s="0">
@@ -6990,7 +6990,7 @@
       <c r="A95" s="0" t="n">
         <v>9.16848755</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="0" t="n">
         <v>0.42868</v>
       </c>
       <c r="C95" s="0">
@@ -7057,7 +7057,7 @@
       <c r="A96" s="0" t="n">
         <v>9.267945299999999</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.4248</v>
       </c>
       <c r="C96" s="0">
@@ -7124,7 +7124,7 @@
       <c r="A97" s="0" t="n">
         <v>9.368123049999999</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="0" t="n">
         <v>0.42099</v>
       </c>
       <c r="C97" s="0">
@@ -7191,7 +7191,7 @@
       <c r="A98" s="0" t="n">
         <v>9.4675808</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="0" t="n">
         <v>0.41724</v>
       </c>
       <c r="C98" s="0">
@@ -7258,7 +7258,7 @@
       <c r="A99" s="0" t="n">
         <v>9.567759499999999</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="0" t="n">
         <v>0.41342</v>
       </c>
       <c r="C99" s="0">
@@ -7325,7 +7325,7 @@
       <c r="A100" s="0" t="n">
         <v>9.6664963</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="0" t="n">
         <v>0.40967</v>
       </c>
       <c r="C100" s="0">
@@ -7392,7 +7392,7 @@
       <c r="A101" s="0" t="n">
         <v>9.766674999999999</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="0" t="n">
         <v>0.40582</v>
       </c>
       <c r="C101" s="0">
@@ -7459,7 +7459,7 @@
       <c r="A102" s="0" t="n">
         <v>9.8668537</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="0" t="n">
         <v>0.40196</v>
       </c>
       <c r="C102" s="0">
@@ -7526,7 +7526,7 @@
       <c r="A103" s="0" t="n">
         <v>9.965590499999999</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="0" t="n">
         <v>0.3981</v>
       </c>
       <c r="C103" s="0">
@@ -7593,7 +7593,7 @@
       <c r="A104" s="0" t="n">
         <v>10.06649015</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="0" t="n">
         <v>0.39425</v>
       </c>
       <c r="C104" s="0">
@@ -7660,7 +7660,7 @@
       <c r="A105" s="0" t="n">
         <v>10.16522695</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="0" t="n">
         <v>0.39047</v>
       </c>
       <c r="C105" s="0">
@@ -7727,7 +7727,7 @@
       <c r="A106" s="0" t="n">
         <v>10.26540565</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="0" t="n">
         <v>0.38658</v>
       </c>
       <c r="C106" s="0">
@@ -7794,7 +7794,7 @@
       <c r="A107" s="0" t="n">
         <v>10.36342145</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="0" t="n">
         <v>0.38265</v>
       </c>
       <c r="C107" s="0">
@@ -7861,7 +7861,7 @@
       <c r="A108" s="0" t="n">
         <v>10.46360015</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="0" t="n">
         <v>0.37875</v>
       </c>
       <c r="C108" s="0">
@@ -7928,7 +7928,7 @@
       <c r="A109" s="0" t="n">
         <v>10.5630579</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="0" t="n">
         <v>0.37484</v>
       </c>
       <c r="C109" s="0">
@@ -7995,7 +7995,7 @@
       <c r="A110" s="0" t="n">
         <v>10.6632366</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="0" t="n">
         <v>0.37093</v>
       </c>
       <c r="C110" s="0">
@@ -8062,7 +8062,7 @@
       <c r="A111" s="0" t="n">
         <v>10.76341535</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="0" t="n">
         <v>0.36691</v>
       </c>
       <c r="C111" s="0">
@@ -8129,7 +8129,7 @@
       <c r="A112" s="0" t="n">
         <v>10.8621521</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="0" t="n">
         <v>0.36298</v>
       </c>
       <c r="C112" s="0">
@@ -8196,7 +8196,7 @@
       <c r="A113" s="0" t="n">
         <v>10.96160985</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.35897</v>
       </c>
       <c r="C113" s="0">
@@ -8263,7 +8263,7 @@
       <c r="A114" s="0" t="n">
         <v>11.0610676</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="0" t="n">
         <v>0.35499</v>
       </c>
       <c r="C114" s="0">
@@ -8330,7 +8330,7 @@
       <c r="A115" s="0" t="n">
         <v>11.1619663</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="0" t="n">
         <v>0.35098</v>
       </c>
       <c r="C115" s="0">
@@ -8397,7 +8397,7 @@
       <c r="A116" s="0" t="n">
         <v>11.2585411</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="0" t="n">
         <v>0.34693</v>
       </c>
       <c r="C116" s="0">
@@ -8464,7 +8464,7 @@
       <c r="A117" s="0" t="n">
         <v>11.3616028</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="0" t="n">
         <v>0.34293</v>
       </c>
       <c r="C117" s="0">
@@ -8531,7 +8531,7 @@
       <c r="A118" s="0" t="n">
         <v>11.4596195</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="0" t="n">
         <v>0.33877</v>
       </c>
       <c r="C118" s="0">
@@ -8598,7 +8598,7 @@
       <c r="A119" s="0" t="n">
         <v>11.56051825</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="0" t="n">
         <v>0.33471</v>
       </c>
       <c r="C119" s="0">
@@ -8665,7 +8665,7 @@
       <c r="A120" s="0" t="n">
         <v>11.65925505</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="0" t="n">
         <v>0.33052</v>
       </c>
       <c r="C120" s="0">
@@ -8732,7 +8732,7 @@
       <c r="A121" s="0" t="n">
         <v>11.75943375</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="0" t="n">
         <v>0.32645</v>
       </c>
       <c r="C121" s="0">
@@ -8799,7 +8799,7 @@
       <c r="A122" s="0" t="n">
         <v>11.8574505</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="0" t="n">
         <v>0.32227</v>
       </c>
       <c r="C122" s="0">
@@ -8866,7 +8866,7 @@
       <c r="A123" s="0" t="n">
         <v>11.9590702</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="0" t="n">
         <v>0.31805</v>
       </c>
       <c r="C123" s="0">
@@ -8933,7 +8933,7 @@
       <c r="A124" s="0" t="n">
         <v>12.05780695</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="0" t="n">
         <v>0.31383</v>
       </c>
       <c r="C124" s="0">
@@ -9000,7 +9000,7 @@
       <c r="A125" s="0" t="n">
         <v>12.1579857</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="0" t="n">
         <v>0.30958</v>
       </c>
       <c r="C125" s="0">
@@ -9067,7 +9067,7 @@
       <c r="A126" s="0" t="n">
         <v>12.25672245</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="0" t="n">
         <v>0.30533</v>
       </c>
       <c r="C126" s="0">
@@ -9134,7 +9134,7 @@
       <c r="A127" s="0" t="n">
         <v>12.35690115</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="0" t="n">
         <v>0.30103</v>
       </c>
       <c r="C127" s="0">
@@ -9201,7 +9201,7 @@
       <c r="A128" s="0" t="n">
         <v>12.4577999</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="0" t="n">
         <v>0.29665</v>
       </c>
       <c r="C128" s="0">
@@ -9268,7 +9268,7 @@
       <c r="A129" s="0" t="n">
         <v>12.55653765</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="0" t="n">
         <v>0.29229</v>
       </c>
       <c r="C129" s="0">
@@ -9335,7 +9335,7 @@
       <c r="A130" s="0" t="n">
         <v>12.6567154</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="0" t="n">
         <v>0.28795</v>
       </c>
       <c r="C130" s="0">
@@ -9402,7 +9402,7 @@
       <c r="A131" s="0" t="n">
         <v>12.7568941</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="0" t="n">
         <v>0.28346</v>
       </c>
       <c r="C131" s="0">
@@ -9469,7 +9469,7 @@
       <c r="A132" s="0" t="n">
         <v>12.85563085</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="0" t="n">
         <v>0.27892</v>
       </c>
       <c r="C132" s="0">
@@ -9536,7 +9536,7 @@
       <c r="A133" s="0" t="n">
         <v>12.95653055</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="0" t="n">
         <v>0.27457</v>
       </c>
       <c r="C133" s="0">
@@ -9603,7 +9603,7 @@
       <c r="A134" s="0" t="n">
         <v>13.05454635</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="0" t="n">
         <v>0.27003</v>
       </c>
       <c r="C134" s="0">
@@ -9670,7 +9670,7 @@
       <c r="A135" s="0" t="n">
         <v>13.15472505</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="0" t="n">
         <v>0.26537</v>
       </c>
       <c r="C135" s="0">
@@ -9737,7 +9737,7 @@
       <c r="A136" s="0" t="n">
         <v>13.2527418</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="0" t="n">
         <v>0.26079</v>
       </c>
       <c r="C136" s="0">
@@ -9804,7 +9804,7 @@
       <c r="A137" s="0" t="n">
         <v>13.35364055</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="0" t="n">
         <v>0.2562</v>
       </c>
       <c r="C137" s="0">
@@ -9871,7 +9871,7 @@
       <c r="A138" s="0" t="n">
         <v>13.45381925</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="0" t="n">
         <v>0.2514</v>
       </c>
       <c r="C138" s="0">
